--- a/test/fixtures/Config_TargetType.xlsx
+++ b/test/fixtures/Config_TargetType.xlsx
@@ -487,7 +487,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>.TargetType</t>
+          <t>_TargetType</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">

--- a/test/fixtures/Config_TargetType.xlsx
+++ b/test/fixtures/Config_TargetType.xlsx
@@ -492,7 +492,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DHL.ITS.RPAForge.SAP.SapConfig</t>
+          <t>CPMForge.SAP.SapConfig</t>
         </is>
       </c>
     </row>
